--- a/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/22_Darlehenskonto_und_Saldenkontrolle.xlsx
+++ b/testakten/filmrechte-sicherungsuebertragung-insolvenz-schwetzingen/04_Finanzierung_Sicherheiten/22_Darlehenskonto_und_Saldenkontrolle.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Darlehenskonto" sheetId="1" r:id="Rfec40c92c6d442a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollsummen" sheetId="2" r:id="R139a4826885e4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Darlehenskonto" sheetId="1" r:id="R96d4481b665d4152"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kontrollsummen" sheetId="2" r:id="Re575acb7c54941f3"/>
   </x:sheets>
 </x:workbook>
 </file>
